--- a/grupos/6BLCM - Estadisticos 20212.xlsx
+++ b/grupos/6BLCM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="146">
   <si>
     <t>Materia</t>
   </si>
@@ -182,21 +182,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
+    <t>Ángel Martínez Gerson Hermenegildo</t>
+  </si>
+  <si>
     <t>Flores González Ángel</t>
   </si>
   <si>
-    <t>Rivera Cruz Ezequiel</t>
-  </si>
-  <si>
-    <t>Ángel Martínez Gerson Hermenegildo</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -209,6 +209,66 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>GUILLEN</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>MERINO</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>VELEZ</t>
+  </si>
+  <si>
+    <t>LINARES</t>
+  </si>
+  <si>
+    <t>TLEHUACTLE</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>VALERDE</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>EDITH</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>DANNA PAOLA</t>
+  </si>
+  <si>
+    <t>JULIO CESAR</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>JUDITH ESTEFANIA</t>
+  </si>
+  <si>
+    <t>ROSARIO DOLORES</t>
+  </si>
+  <si>
     <t>AMABLE</t>
   </si>
   <si>
@@ -230,48 +290,27 @@
     <t>GROTH</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUILLEN</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
     <t>HEREDIA</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
     <t>JUAREZ</t>
   </si>
   <si>
-    <t>LEON</t>
-  </si>
-  <si>
     <t>LIMA</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>MERINO</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
     <t>NARVAEZ</t>
   </si>
   <si>
     <t>PAZ</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>PERALTA</t>
   </si>
   <si>
@@ -293,9 +332,6 @@
     <t>TEZOCO</t>
   </si>
   <si>
-    <t>VELEZ</t>
-  </si>
-  <si>
     <t>LARA</t>
   </si>
   <si>
@@ -311,9 +347,6 @@
     <t>VILLANUEVA</t>
   </si>
   <si>
-    <t>LINARES</t>
-  </si>
-  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
@@ -326,9 +359,6 @@
     <t>FLORES</t>
   </si>
   <si>
-    <t>TLEHUACTLE</t>
-  </si>
-  <si>
     <t>MORO</t>
   </si>
   <si>
@@ -338,15 +368,6 @@
     <t>TORRES</t>
   </si>
   <si>
-    <t>VALERDE</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
     <t>BERNABE</t>
   </si>
   <si>
@@ -383,9 +404,6 @@
     <t>GUADALUPE ABRIL</t>
   </si>
   <si>
-    <t>EDITH</t>
-  </si>
-  <si>
     <t>KEVIN JETHZAEL</t>
   </si>
   <si>
@@ -398,27 +416,15 @@
     <t>JOSE GUILLERMO</t>
   </si>
   <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
     <t>DENISSE</t>
   </si>
   <si>
-    <t>DANNA PAOLA</t>
-  </si>
-  <si>
     <t>GUILLERMO UBALDO</t>
   </si>
   <si>
     <t>DIANA</t>
   </si>
   <si>
-    <t>JULIO CESAR</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
     <t>ARIEL</t>
   </si>
   <si>
@@ -434,9 +440,6 @@
     <t>JANETH</t>
   </si>
   <si>
-    <t>JUDITH ESTEFANIA</t>
-  </si>
-  <si>
     <t>MILKA</t>
   </si>
   <si>
@@ -453,9 +456,6 @@
   </si>
   <si>
     <t>ALAN YAMIL</t>
-  </si>
-  <si>
-    <t>ROSARIO DOLORES</t>
   </si>
 </sst>
 </file>
@@ -947,16 +947,16 @@
         <v>10</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H4">
         <v>-1</v>
@@ -1001,16 +1001,16 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1024,16 +1024,16 @@
         <v>10</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H5">
         <v>-1</v>
@@ -1078,16 +1078,16 @@
         <v>10</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1101,16 +1101,16 @@
         <v>10</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H6">
         <v>-1</v>
@@ -1155,16 +1155,16 @@
         <v>10</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1178,16 +1178,16 @@
         <v>10</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H7">
         <v>-1</v>
@@ -1232,16 +1232,16 @@
         <v>10</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1255,16 +1255,16 @@
         <v>9</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H8">
         <v>-1</v>
@@ -1309,16 +1309,16 @@
         <v>9</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1332,16 +1332,16 @@
         <v>10</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H9">
         <v>-1</v>
@@ -1386,16 +1386,16 @@
         <v>10</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1409,16 +1409,16 @@
         <v>10</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H10">
         <v>-1</v>
@@ -1463,16 +1463,16 @@
         <v>10</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1486,16 +1486,16 @@
         <v>9</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H11">
         <v>-1</v>
@@ -1540,16 +1540,16 @@
         <v>9</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1563,16 +1563,16 @@
         <v>6</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E12">
         <v>-1</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H12">
         <v>-1</v>
@@ -1617,16 +1617,16 @@
         <v>6</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>-1</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1640,16 +1640,16 @@
         <v>8</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H13">
         <v>-1</v>
@@ -1694,16 +1694,16 @@
         <v>8</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1717,16 +1717,16 @@
         <v>10</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H14">
         <v>-1</v>
@@ -1771,16 +1771,16 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1794,16 +1794,16 @@
         <v>9</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H15">
         <v>-1</v>
@@ -1848,16 +1848,16 @@
         <v>9</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1871,16 +1871,16 @@
         <v>9</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H16">
         <v>-1</v>
@@ -1925,16 +1925,16 @@
         <v>9</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1948,16 +1948,16 @@
         <v>9</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E17">
         <v>-1</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H17">
         <v>-1</v>
@@ -2002,16 +2002,16 @@
         <v>9</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W17">
         <v>-1</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2025,16 +2025,16 @@
         <v>9</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H18">
         <v>-1</v>
@@ -2079,16 +2079,16 @@
         <v>9</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2108,10 +2108,10 @@
         <v>-1</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H19">
         <v>-1</v>
@@ -2162,10 +2162,10 @@
         <v>-1</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2179,16 +2179,16 @@
         <v>9</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H20">
         <v>-1</v>
@@ -2233,16 +2233,16 @@
         <v>9</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2256,16 +2256,16 @@
         <v>8</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H21">
         <v>-1</v>
@@ -2310,16 +2310,16 @@
         <v>8</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2333,16 +2333,16 @@
         <v>6</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E22">
         <v>-1</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H22">
         <v>-1</v>
@@ -2387,16 +2387,16 @@
         <v>6</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W22">
         <v>-1</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2413,13 +2413,13 @@
         <v>-1</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H23">
         <v>-1</v>
@@ -2467,13 +2467,13 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2487,16 +2487,16 @@
         <v>8</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H24">
         <v>-1</v>
@@ -2541,16 +2541,16 @@
         <v>8</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2564,16 +2564,16 @@
         <v>10</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H25">
         <v>-1</v>
@@ -2618,16 +2618,16 @@
         <v>10</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2641,16 +2641,16 @@
         <v>10</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H26">
         <v>-1</v>
@@ -2695,16 +2695,16 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2718,16 +2718,16 @@
         <v>10</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H27">
         <v>-1</v>
@@ -2772,16 +2772,16 @@
         <v>10</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2795,16 +2795,16 @@
         <v>8</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H28">
         <v>-1</v>
@@ -2849,16 +2849,16 @@
         <v>8</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2872,16 +2872,16 @@
         <v>6</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E29">
         <v>-1</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H29">
         <v>-1</v>
@@ -2926,16 +2926,16 @@
         <v>6</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W29">
         <v>-1</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2949,16 +2949,16 @@
         <v>10</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H30">
         <v>-1</v>
@@ -3003,16 +3003,16 @@
         <v>10</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3026,16 +3026,16 @@
         <v>9</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H31">
         <v>-1</v>
@@ -3080,16 +3080,16 @@
         <v>9</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3103,16 +3103,16 @@
         <v>10</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H32">
         <v>-1</v>
@@ -3157,16 +3157,16 @@
         <v>10</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3180,16 +3180,16 @@
         <v>9</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H33">
         <v>-1</v>
@@ -3234,16 +3234,16 @@
         <v>9</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3257,16 +3257,16 @@
         <v>10</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H34">
         <v>-1</v>
@@ -3311,16 +3311,16 @@
         <v>10</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3334,16 +3334,16 @@
         <v>10</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H35">
         <v>-1</v>
@@ -3388,16 +3388,16 @@
         <v>10</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3411,16 +3411,16 @@
         <v>10</v>
       </c>
       <c r="D36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E36">
         <v>-1</v>
       </c>
       <c r="F36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H36">
         <v>-1</v>
@@ -3465,16 +3465,16 @@
         <v>10</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W36">
         <v>-1</v>
       </c>
       <c r="X36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3530,7 +3530,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
@@ -3539,27 +3539,30 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>8.1</v>
+      </c>
       <c r="I2">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -3568,27 +3571,30 @@
         <v>33</v>
       </c>
       <c r="D3">
+        <v>29</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>87.88</v>
+      </c>
+      <c r="G3">
+        <v>12.12</v>
+      </c>
+      <c r="H3">
+        <v>8.6</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="E3">
+      <c r="J3">
         <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>33</v>
-      </c>
-      <c r="J3">
-        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -3597,27 +3603,30 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>93.94</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
+      <c r="H4">
+        <v>9.5</v>
+      </c>
       <c r="I4">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -3626,30 +3635,33 @@
         <v>33</v>
       </c>
       <c r="D5">
+        <v>32</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>96.97</v>
+      </c>
+      <c r="G5">
+        <v>3.03</v>
+      </c>
+      <c r="H5">
+        <v>9</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="E5">
+      <c r="J5">
         <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>33</v>
-      </c>
-      <c r="J5">
-        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C6">
         <v>33</v>
@@ -3678,7 +3690,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>58</v>
@@ -3687,19 +3699,19 @@
         <v>33</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>96.97</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3715,7 +3727,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F133"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3744,19 +3756,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920186</v>
+        <v>19330051920195</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
         <v>54</v>
@@ -3764,39 +3776,39 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920186</v>
+        <v>19330051920200</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920186</v>
+        <v>19330051920202</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
         <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
         <v>56</v>
@@ -3804,39 +3816,39 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920186</v>
+        <v>19330051920202</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
         <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920185</v>
+        <v>19330051920206</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
         <v>54</v>
@@ -3844,2542 +3856,62 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920185</v>
+        <v>19330051920207</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920185</v>
+        <v>19330051920214</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920185</v>
+        <v>18330051920351</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>19330051920187</v>
-      </c>
-      <c r="B10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" t="s">
-        <v>93</v>
-      </c>
-      <c r="D10" t="s">
-        <v>115</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>19330051920187</v>
-      </c>
-      <c r="B11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" t="s">
-        <v>93</v>
-      </c>
-      <c r="D11" t="s">
-        <v>115</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>19330051920187</v>
-      </c>
-      <c r="B12" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" t="s">
-        <v>93</v>
-      </c>
-      <c r="D12" t="s">
-        <v>115</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>19330051920187</v>
-      </c>
-      <c r="B13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" t="s">
-        <v>93</v>
-      </c>
-      <c r="D13" t="s">
-        <v>115</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>19330051920189</v>
-      </c>
-      <c r="B14" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" t="s">
-        <v>94</v>
-      </c>
-      <c r="D14" t="s">
-        <v>116</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>19330051920189</v>
-      </c>
-      <c r="B15" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" t="s">
-        <v>94</v>
-      </c>
-      <c r="D15" t="s">
-        <v>116</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>19330051920189</v>
-      </c>
-      <c r="B16" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D16" t="s">
-        <v>116</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>19330051920189</v>
-      </c>
-      <c r="B17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" t="s">
-        <v>94</v>
-      </c>
-      <c r="D17" t="s">
-        <v>116</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>19330051920190</v>
-      </c>
-      <c r="B18" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" t="s">
-        <v>89</v>
-      </c>
-      <c r="D18" t="s">
-        <v>117</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>19330051920190</v>
-      </c>
-      <c r="B19" t="s">
-        <v>67</v>
-      </c>
-      <c r="C19" t="s">
-        <v>89</v>
-      </c>
-      <c r="D19" t="s">
-        <v>117</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>19330051920190</v>
-      </c>
-      <c r="B20" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" t="s">
-        <v>89</v>
-      </c>
-      <c r="D20" t="s">
-        <v>117</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>19330051920190</v>
-      </c>
-      <c r="B21" t="s">
-        <v>67</v>
-      </c>
-      <c r="C21" t="s">
-        <v>89</v>
-      </c>
-      <c r="D21" t="s">
-        <v>117</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>19330051920192</v>
-      </c>
-      <c r="B22" t="s">
-        <v>68</v>
-      </c>
-      <c r="C22" t="s">
-        <v>78</v>
-      </c>
-      <c r="D22" t="s">
-        <v>118</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>19330051920192</v>
-      </c>
-      <c r="B23" t="s">
-        <v>68</v>
-      </c>
-      <c r="C23" t="s">
-        <v>78</v>
-      </c>
-      <c r="D23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>19330051920192</v>
-      </c>
-      <c r="B24" t="s">
-        <v>68</v>
-      </c>
-      <c r="C24" t="s">
-        <v>78</v>
-      </c>
-      <c r="D24" t="s">
-        <v>118</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>19330051920192</v>
-      </c>
-      <c r="B25" t="s">
-        <v>68</v>
-      </c>
-      <c r="C25" t="s">
-        <v>78</v>
-      </c>
-      <c r="D25" t="s">
-        <v>118</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>19330051920194</v>
-      </c>
-      <c r="B26" t="s">
-        <v>69</v>
-      </c>
-      <c r="C26" t="s">
-        <v>95</v>
-      </c>
-      <c r="D26" t="s">
-        <v>119</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>19330051920194</v>
-      </c>
-      <c r="B27" t="s">
-        <v>69</v>
-      </c>
-      <c r="C27" t="s">
-        <v>95</v>
-      </c>
-      <c r="D27" t="s">
-        <v>119</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>19330051920194</v>
-      </c>
-      <c r="B28" t="s">
-        <v>69</v>
-      </c>
-      <c r="C28" t="s">
-        <v>95</v>
-      </c>
-      <c r="D28" t="s">
-        <v>119</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>19330051920194</v>
-      </c>
-      <c r="B29" t="s">
-        <v>69</v>
-      </c>
-      <c r="C29" t="s">
-        <v>95</v>
-      </c>
-      <c r="D29" t="s">
-        <v>119</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>19330051920193</v>
-      </c>
-      <c r="B30" t="s">
-        <v>70</v>
-      </c>
-      <c r="C30" t="s">
-        <v>96</v>
-      </c>
-      <c r="D30" t="s">
-        <v>120</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>19330051920193</v>
-      </c>
-      <c r="B31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C31" t="s">
-        <v>96</v>
-      </c>
-      <c r="D31" t="s">
-        <v>120</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>19330051920193</v>
-      </c>
-      <c r="B32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C32" t="s">
-        <v>96</v>
-      </c>
-      <c r="D32" t="s">
-        <v>120</v>
-      </c>
-      <c r="E32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>19330051920193</v>
-      </c>
-      <c r="B33" t="s">
-        <v>70</v>
-      </c>
-      <c r="C33" t="s">
-        <v>96</v>
-      </c>
-      <c r="D33" t="s">
-        <v>120</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>19330051920195</v>
-      </c>
-      <c r="B34" t="s">
-        <v>71</v>
-      </c>
-      <c r="C34" t="s">
-        <v>97</v>
-      </c>
-      <c r="D34" t="s">
-        <v>121</v>
-      </c>
-      <c r="E34" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>19330051920195</v>
-      </c>
-      <c r="B35" t="s">
-        <v>71</v>
-      </c>
-      <c r="C35" t="s">
-        <v>97</v>
-      </c>
-      <c r="D35" t="s">
-        <v>121</v>
-      </c>
-      <c r="E35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>19330051920195</v>
-      </c>
-      <c r="B36" t="s">
-        <v>71</v>
-      </c>
-      <c r="C36" t="s">
-        <v>97</v>
-      </c>
-      <c r="D36" t="s">
-        <v>121</v>
-      </c>
-      <c r="E36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>19330051920195</v>
-      </c>
-      <c r="B37" t="s">
-        <v>71</v>
-      </c>
-      <c r="C37" t="s">
-        <v>97</v>
-      </c>
-      <c r="D37" t="s">
-        <v>121</v>
-      </c>
-      <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>19330051920197</v>
-      </c>
-      <c r="B38" t="s">
-        <v>72</v>
-      </c>
-      <c r="C38" t="s">
-        <v>98</v>
-      </c>
-      <c r="D38" t="s">
-        <v>122</v>
-      </c>
-      <c r="E38" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>19330051920197</v>
-      </c>
-      <c r="B39" t="s">
-        <v>72</v>
-      </c>
-      <c r="C39" t="s">
-        <v>98</v>
-      </c>
-      <c r="D39" t="s">
-        <v>122</v>
-      </c>
-      <c r="E39" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>19330051920197</v>
-      </c>
-      <c r="B40" t="s">
-        <v>72</v>
-      </c>
-      <c r="C40" t="s">
-        <v>98</v>
-      </c>
-      <c r="D40" t="s">
-        <v>122</v>
-      </c>
-      <c r="E40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>19330051920197</v>
-      </c>
-      <c r="B41" t="s">
-        <v>72</v>
-      </c>
-      <c r="C41" t="s">
-        <v>98</v>
-      </c>
-      <c r="D41" t="s">
-        <v>122</v>
-      </c>
-      <c r="E41" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>19330051920196</v>
-      </c>
-      <c r="B42" t="s">
-        <v>73</v>
-      </c>
-      <c r="C42" t="s">
-        <v>99</v>
-      </c>
-      <c r="D42" t="s">
-        <v>123</v>
-      </c>
-      <c r="E42" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>19330051920196</v>
-      </c>
-      <c r="B43" t="s">
-        <v>73</v>
-      </c>
-      <c r="C43" t="s">
-        <v>99</v>
-      </c>
-      <c r="D43" t="s">
-        <v>123</v>
-      </c>
-      <c r="E43" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>19330051920196</v>
-      </c>
-      <c r="B44" t="s">
-        <v>73</v>
-      </c>
-      <c r="C44" t="s">
-        <v>99</v>
-      </c>
-      <c r="D44" t="s">
-        <v>123</v>
-      </c>
-      <c r="E44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>19330051920196</v>
-      </c>
-      <c r="B45" t="s">
-        <v>73</v>
-      </c>
-      <c r="C45" t="s">
-        <v>99</v>
-      </c>
-      <c r="D45" t="s">
-        <v>123</v>
-      </c>
-      <c r="E45" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>19330051920198</v>
-      </c>
-      <c r="B46" t="s">
-        <v>72</v>
-      </c>
-      <c r="C46" t="s">
-        <v>100</v>
-      </c>
-      <c r="D46" t="s">
-        <v>124</v>
-      </c>
-      <c r="E46" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>19330051920198</v>
-      </c>
-      <c r="B47" t="s">
-        <v>72</v>
-      </c>
-      <c r="C47" t="s">
-        <v>100</v>
-      </c>
-      <c r="D47" t="s">
-        <v>124</v>
-      </c>
-      <c r="E47" t="s">
-        <v>7</v>
-      </c>
-      <c r="F47" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>19330051920198</v>
-      </c>
-      <c r="B48" t="s">
-        <v>72</v>
-      </c>
-      <c r="C48" t="s">
-        <v>100</v>
-      </c>
-      <c r="D48" t="s">
-        <v>124</v>
-      </c>
-      <c r="E48" t="s">
-        <v>9</v>
-      </c>
-      <c r="F48" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>19330051920198</v>
-      </c>
-      <c r="B49" t="s">
-        <v>72</v>
-      </c>
-      <c r="C49" t="s">
-        <v>100</v>
-      </c>
-      <c r="D49" t="s">
-        <v>124</v>
-      </c>
-      <c r="E49" t="s">
-        <v>8</v>
-      </c>
-      <c r="F49" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>19330051920199</v>
-      </c>
-      <c r="B50" t="s">
-        <v>74</v>
-      </c>
-      <c r="C50" t="s">
-        <v>101</v>
-      </c>
-      <c r="D50" t="s">
-        <v>125</v>
-      </c>
-      <c r="E50" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>19330051920199</v>
-      </c>
-      <c r="B51" t="s">
-        <v>74</v>
-      </c>
-      <c r="C51" t="s">
-        <v>101</v>
-      </c>
-      <c r="D51" t="s">
-        <v>125</v>
-      </c>
-      <c r="E51" t="s">
-        <v>7</v>
-      </c>
-      <c r="F51" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>19330051920199</v>
-      </c>
-      <c r="B52" t="s">
-        <v>74</v>
-      </c>
-      <c r="C52" t="s">
-        <v>101</v>
-      </c>
-      <c r="D52" t="s">
-        <v>125</v>
-      </c>
-      <c r="E52" t="s">
-        <v>9</v>
-      </c>
-      <c r="F52" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>19330051920199</v>
-      </c>
-      <c r="B53" t="s">
-        <v>74</v>
-      </c>
-      <c r="C53" t="s">
-        <v>101</v>
-      </c>
-      <c r="D53" t="s">
-        <v>125</v>
-      </c>
-      <c r="E53" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>19330051920200</v>
-      </c>
-      <c r="B54" t="s">
-        <v>74</v>
-      </c>
-      <c r="C54" t="s">
-        <v>102</v>
-      </c>
-      <c r="D54" t="s">
-        <v>126</v>
-      </c>
-      <c r="E54" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>19330051920200</v>
-      </c>
-      <c r="B55" t="s">
-        <v>74</v>
-      </c>
-      <c r="C55" t="s">
-        <v>102</v>
-      </c>
-      <c r="D55" t="s">
-        <v>126</v>
-      </c>
-      <c r="E55" t="s">
-        <v>7</v>
-      </c>
-      <c r="F55" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>19330051920200</v>
-      </c>
-      <c r="B56" t="s">
-        <v>74</v>
-      </c>
-      <c r="C56" t="s">
-        <v>102</v>
-      </c>
-      <c r="D56" t="s">
-        <v>126</v>
-      </c>
-      <c r="E56" t="s">
-        <v>9</v>
-      </c>
-      <c r="F56" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>19330051920200</v>
-      </c>
-      <c r="B57" t="s">
-        <v>74</v>
-      </c>
-      <c r="C57" t="s">
-        <v>102</v>
-      </c>
-      <c r="D57" t="s">
-        <v>126</v>
-      </c>
-      <c r="E57" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>19330051920201</v>
-      </c>
-      <c r="B58" t="s">
-        <v>75</v>
-      </c>
-      <c r="C58" t="s">
-        <v>103</v>
-      </c>
-      <c r="D58" t="s">
-        <v>127</v>
-      </c>
-      <c r="E58" t="s">
-        <v>10</v>
-      </c>
-      <c r="F58" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>19330051920201</v>
-      </c>
-      <c r="B59" t="s">
-        <v>75</v>
-      </c>
-      <c r="C59" t="s">
-        <v>103</v>
-      </c>
-      <c r="D59" t="s">
-        <v>127</v>
-      </c>
-      <c r="E59" t="s">
-        <v>7</v>
-      </c>
-      <c r="F59" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>19330051920201</v>
-      </c>
-      <c r="B60" t="s">
-        <v>75</v>
-      </c>
-      <c r="C60" t="s">
-        <v>103</v>
-      </c>
-      <c r="D60" t="s">
-        <v>127</v>
-      </c>
-      <c r="E60" t="s">
-        <v>9</v>
-      </c>
-      <c r="F60" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>19330051920201</v>
-      </c>
-      <c r="B61" t="s">
-        <v>75</v>
-      </c>
-      <c r="C61" t="s">
-        <v>103</v>
-      </c>
-      <c r="D61" t="s">
-        <v>127</v>
-      </c>
-      <c r="E61" t="s">
-        <v>8</v>
-      </c>
-      <c r="F61" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>19330051920202</v>
-      </c>
-      <c r="B62" t="s">
-        <v>76</v>
-      </c>
-      <c r="C62" t="s">
-        <v>70</v>
-      </c>
-      <c r="D62" t="s">
-        <v>128</v>
-      </c>
-      <c r="E62" t="s">
-        <v>10</v>
-      </c>
-      <c r="F62" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>19330051920202</v>
-      </c>
-      <c r="B63" t="s">
-        <v>76</v>
-      </c>
-      <c r="C63" t="s">
-        <v>70</v>
-      </c>
-      <c r="D63" t="s">
-        <v>128</v>
-      </c>
-      <c r="E63" t="s">
-        <v>7</v>
-      </c>
-      <c r="F63" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>19330051920202</v>
-      </c>
-      <c r="B64" t="s">
-        <v>76</v>
-      </c>
-      <c r="C64" t="s">
-        <v>70</v>
-      </c>
-      <c r="D64" t="s">
-        <v>128</v>
-      </c>
-      <c r="E64" t="s">
-        <v>9</v>
-      </c>
-      <c r="F64" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>19330051920202</v>
-      </c>
-      <c r="B65" t="s">
-        <v>76</v>
-      </c>
-      <c r="C65" t="s">
-        <v>70</v>
-      </c>
-      <c r="D65" t="s">
-        <v>128</v>
-      </c>
-      <c r="E65" t="s">
-        <v>8</v>
-      </c>
-      <c r="F65" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>19330051920203</v>
-      </c>
-      <c r="B66" t="s">
-        <v>77</v>
-      </c>
-      <c r="C66" t="s">
-        <v>104</v>
-      </c>
-      <c r="D66" t="s">
-        <v>129</v>
-      </c>
-      <c r="E66" t="s">
-        <v>10</v>
-      </c>
-      <c r="F66" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>19330051920203</v>
-      </c>
-      <c r="B67" t="s">
-        <v>77</v>
-      </c>
-      <c r="C67" t="s">
-        <v>104</v>
-      </c>
-      <c r="D67" t="s">
-        <v>129</v>
-      </c>
-      <c r="E67" t="s">
-        <v>7</v>
-      </c>
-      <c r="F67" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>19330051920203</v>
-      </c>
-      <c r="B68" t="s">
-        <v>77</v>
-      </c>
-      <c r="C68" t="s">
-        <v>104</v>
-      </c>
-      <c r="D68" t="s">
-        <v>129</v>
-      </c>
-      <c r="E68" t="s">
-        <v>9</v>
-      </c>
-      <c r="F68" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>19330051920203</v>
-      </c>
-      <c r="B69" t="s">
-        <v>77</v>
-      </c>
-      <c r="C69" t="s">
-        <v>104</v>
-      </c>
-      <c r="D69" t="s">
-        <v>129</v>
-      </c>
-      <c r="E69" t="s">
-        <v>8</v>
-      </c>
-      <c r="F69" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>19330051920204</v>
-      </c>
-      <c r="B70" t="s">
-        <v>78</v>
-      </c>
-      <c r="C70" t="s">
-        <v>105</v>
-      </c>
-      <c r="D70" t="s">
-        <v>130</v>
-      </c>
-      <c r="E70" t="s">
-        <v>10</v>
-      </c>
-      <c r="F70" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>19330051920204</v>
-      </c>
-      <c r="B71" t="s">
-        <v>78</v>
-      </c>
-      <c r="C71" t="s">
-        <v>105</v>
-      </c>
-      <c r="D71" t="s">
-        <v>130</v>
-      </c>
-      <c r="E71" t="s">
-        <v>7</v>
-      </c>
-      <c r="F71" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>19330051920204</v>
-      </c>
-      <c r="B72" t="s">
-        <v>78</v>
-      </c>
-      <c r="C72" t="s">
-        <v>105</v>
-      </c>
-      <c r="D72" t="s">
-        <v>130</v>
-      </c>
-      <c r="E72" t="s">
-        <v>9</v>
-      </c>
-      <c r="F72" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>19330051920204</v>
-      </c>
-      <c r="B73" t="s">
-        <v>78</v>
-      </c>
-      <c r="C73" t="s">
-        <v>105</v>
-      </c>
-      <c r="D73" t="s">
-        <v>130</v>
-      </c>
-      <c r="E73" t="s">
-        <v>8</v>
-      </c>
-      <c r="F73" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>19330051920206</v>
-      </c>
-      <c r="B74" t="s">
-        <v>79</v>
-      </c>
-      <c r="C74" t="s">
-        <v>106</v>
-      </c>
-      <c r="D74" t="s">
-        <v>131</v>
-      </c>
-      <c r="E74" t="s">
-        <v>10</v>
-      </c>
-      <c r="F74" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>19330051920206</v>
-      </c>
-      <c r="B75" t="s">
-        <v>79</v>
-      </c>
-      <c r="C75" t="s">
-        <v>106</v>
-      </c>
-      <c r="D75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E75" t="s">
-        <v>7</v>
-      </c>
-      <c r="F75" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>19330051920206</v>
-      </c>
-      <c r="B76" t="s">
-        <v>79</v>
-      </c>
-      <c r="C76" t="s">
-        <v>106</v>
-      </c>
-      <c r="D76" t="s">
-        <v>131</v>
-      </c>
-      <c r="E76" t="s">
-        <v>9</v>
-      </c>
-      <c r="F76" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>19330051920206</v>
-      </c>
-      <c r="B77" t="s">
-        <v>79</v>
-      </c>
-      <c r="C77" t="s">
-        <v>106</v>
-      </c>
-      <c r="D77" t="s">
-        <v>131</v>
-      </c>
-      <c r="E77" t="s">
-        <v>8</v>
-      </c>
-      <c r="F77" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>19330051920207</v>
-      </c>
-      <c r="B78" t="s">
-        <v>80</v>
-      </c>
-      <c r="C78" t="s">
-        <v>107</v>
-      </c>
-      <c r="D78" t="s">
-        <v>132</v>
-      </c>
-      <c r="E78" t="s">
-        <v>10</v>
-      </c>
-      <c r="F78" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>19330051920207</v>
-      </c>
-      <c r="B79" t="s">
-        <v>80</v>
-      </c>
-      <c r="C79" t="s">
-        <v>107</v>
-      </c>
-      <c r="D79" t="s">
-        <v>132</v>
-      </c>
-      <c r="E79" t="s">
-        <v>7</v>
-      </c>
-      <c r="F79" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>19330051920207</v>
-      </c>
-      <c r="B80" t="s">
-        <v>80</v>
-      </c>
-      <c r="C80" t="s">
-        <v>107</v>
-      </c>
-      <c r="D80" t="s">
-        <v>132</v>
-      </c>
-      <c r="E80" t="s">
-        <v>9</v>
-      </c>
-      <c r="F80" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>19330051920207</v>
-      </c>
-      <c r="B81" t="s">
-        <v>80</v>
-      </c>
-      <c r="C81" t="s">
-        <v>107</v>
-      </c>
-      <c r="D81" t="s">
-        <v>132</v>
-      </c>
-      <c r="E81" t="s">
-        <v>8</v>
-      </c>
-      <c r="F81" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>19330051920209</v>
-      </c>
-      <c r="B82" t="s">
-        <v>81</v>
-      </c>
-      <c r="C82" t="s">
-        <v>83</v>
-      </c>
-      <c r="D82" t="s">
-        <v>133</v>
-      </c>
-      <c r="E82" t="s">
-        <v>10</v>
-      </c>
-      <c r="F82" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>19330051920209</v>
-      </c>
-      <c r="B83" t="s">
-        <v>81</v>
-      </c>
-      <c r="C83" t="s">
-        <v>83</v>
-      </c>
-      <c r="D83" t="s">
-        <v>133</v>
-      </c>
-      <c r="E83" t="s">
-        <v>7</v>
-      </c>
-      <c r="F83" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>19330051920209</v>
-      </c>
-      <c r="B84" t="s">
-        <v>81</v>
-      </c>
-      <c r="C84" t="s">
-        <v>83</v>
-      </c>
-      <c r="D84" t="s">
-        <v>133</v>
-      </c>
-      <c r="E84" t="s">
-        <v>9</v>
-      </c>
-      <c r="F84" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>19330051920209</v>
-      </c>
-      <c r="B85" t="s">
-        <v>81</v>
-      </c>
-      <c r="C85" t="s">
-        <v>83</v>
-      </c>
-      <c r="D85" t="s">
-        <v>133</v>
-      </c>
-      <c r="E85" t="s">
-        <v>8</v>
-      </c>
-      <c r="F85" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>19330051920211</v>
-      </c>
-      <c r="B86" t="s">
-        <v>82</v>
-      </c>
-      <c r="C86" t="s">
-        <v>101</v>
-      </c>
-      <c r="D86" t="s">
-        <v>134</v>
-      </c>
-      <c r="E86" t="s">
-        <v>10</v>
-      </c>
-      <c r="F86" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>19330051920211</v>
-      </c>
-      <c r="B87" t="s">
-        <v>82</v>
-      </c>
-      <c r="C87" t="s">
-        <v>101</v>
-      </c>
-      <c r="D87" t="s">
-        <v>134</v>
-      </c>
-      <c r="E87" t="s">
-        <v>7</v>
-      </c>
-      <c r="F87" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>19330051920211</v>
-      </c>
-      <c r="B88" t="s">
-        <v>82</v>
-      </c>
-      <c r="C88" t="s">
-        <v>101</v>
-      </c>
-      <c r="D88" t="s">
-        <v>134</v>
-      </c>
-      <c r="E88" t="s">
-        <v>9</v>
-      </c>
-      <c r="F88" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>19330051920211</v>
-      </c>
-      <c r="B89" t="s">
-        <v>82</v>
-      </c>
-      <c r="C89" t="s">
-        <v>101</v>
-      </c>
-      <c r="D89" t="s">
-        <v>134</v>
-      </c>
-      <c r="E89" t="s">
-        <v>8</v>
-      </c>
-      <c r="F89" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>19330051920215</v>
-      </c>
-      <c r="B90" t="s">
-        <v>83</v>
-      </c>
-      <c r="C90" t="s">
-        <v>72</v>
-      </c>
-      <c r="D90" t="s">
-        <v>135</v>
-      </c>
-      <c r="E90" t="s">
-        <v>10</v>
-      </c>
-      <c r="F90" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>19330051920215</v>
-      </c>
-      <c r="B91" t="s">
-        <v>83</v>
-      </c>
-      <c r="C91" t="s">
-        <v>72</v>
-      </c>
-      <c r="D91" t="s">
-        <v>135</v>
-      </c>
-      <c r="E91" t="s">
-        <v>7</v>
-      </c>
-      <c r="F91" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>19330051920215</v>
-      </c>
-      <c r="B92" t="s">
-        <v>83</v>
-      </c>
-      <c r="C92" t="s">
-        <v>72</v>
-      </c>
-      <c r="D92" t="s">
-        <v>135</v>
-      </c>
-      <c r="E92" t="s">
-        <v>9</v>
-      </c>
-      <c r="F92" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>19330051920215</v>
-      </c>
-      <c r="B93" t="s">
-        <v>83</v>
-      </c>
-      <c r="C93" t="s">
-        <v>72</v>
-      </c>
-      <c r="D93" t="s">
-        <v>135</v>
-      </c>
-      <c r="E93" t="s">
-        <v>8</v>
-      </c>
-      <c r="F93" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>19330051920212</v>
-      </c>
-      <c r="B94" t="s">
-        <v>84</v>
-      </c>
-      <c r="C94" t="s">
-        <v>72</v>
-      </c>
-      <c r="D94" t="s">
-        <v>136</v>
-      </c>
-      <c r="E94" t="s">
-        <v>10</v>
-      </c>
-      <c r="F94" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>19330051920212</v>
-      </c>
-      <c r="B95" t="s">
-        <v>84</v>
-      </c>
-      <c r="C95" t="s">
-        <v>72</v>
-      </c>
-      <c r="D95" t="s">
-        <v>136</v>
-      </c>
-      <c r="E95" t="s">
-        <v>7</v>
-      </c>
-      <c r="F95" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>19330051920212</v>
-      </c>
-      <c r="B96" t="s">
-        <v>84</v>
-      </c>
-      <c r="C96" t="s">
-        <v>72</v>
-      </c>
-      <c r="D96" t="s">
-        <v>136</v>
-      </c>
-      <c r="E96" t="s">
-        <v>9</v>
-      </c>
-      <c r="F96" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97">
-        <v>19330051920212</v>
-      </c>
-      <c r="B97" t="s">
-        <v>84</v>
-      </c>
-      <c r="C97" t="s">
-        <v>72</v>
-      </c>
-      <c r="D97" t="s">
-        <v>136</v>
-      </c>
-      <c r="E97" t="s">
-        <v>8</v>
-      </c>
-      <c r="F97" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98">
-        <v>19330051920213</v>
-      </c>
-      <c r="B98" t="s">
-        <v>83</v>
-      </c>
-      <c r="C98" t="s">
-        <v>85</v>
-      </c>
-      <c r="D98" t="s">
-        <v>137</v>
-      </c>
-      <c r="E98" t="s">
-        <v>10</v>
-      </c>
-      <c r="F98" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99">
-        <v>19330051920213</v>
-      </c>
-      <c r="B99" t="s">
-        <v>83</v>
-      </c>
-      <c r="C99" t="s">
-        <v>85</v>
-      </c>
-      <c r="D99" t="s">
-        <v>137</v>
-      </c>
-      <c r="E99" t="s">
-        <v>7</v>
-      </c>
-      <c r="F99" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="A100">
-        <v>19330051920213</v>
-      </c>
-      <c r="B100" t="s">
-        <v>83</v>
-      </c>
-      <c r="C100" t="s">
-        <v>85</v>
-      </c>
-      <c r="D100" t="s">
-        <v>137</v>
-      </c>
-      <c r="E100" t="s">
-        <v>9</v>
-      </c>
-      <c r="F100" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="A101">
-        <v>19330051920213</v>
-      </c>
-      <c r="B101" t="s">
-        <v>83</v>
-      </c>
-      <c r="C101" t="s">
-        <v>85</v>
-      </c>
-      <c r="D101" t="s">
-        <v>137</v>
-      </c>
-      <c r="E101" t="s">
-        <v>8</v>
-      </c>
-      <c r="F101" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="A102">
-        <v>19330051920214</v>
-      </c>
-      <c r="B102" t="s">
-        <v>83</v>
-      </c>
-      <c r="C102" t="s">
-        <v>108</v>
-      </c>
-      <c r="D102" t="s">
-        <v>138</v>
-      </c>
-      <c r="E102" t="s">
-        <v>10</v>
-      </c>
-      <c r="F102" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="A103">
-        <v>19330051920214</v>
-      </c>
-      <c r="B103" t="s">
-        <v>83</v>
-      </c>
-      <c r="C103" t="s">
-        <v>108</v>
-      </c>
-      <c r="D103" t="s">
-        <v>138</v>
-      </c>
-      <c r="E103" t="s">
-        <v>7</v>
-      </c>
-      <c r="F103" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
-      <c r="A104">
-        <v>19330051920214</v>
-      </c>
-      <c r="B104" t="s">
-        <v>83</v>
-      </c>
-      <c r="C104" t="s">
-        <v>108</v>
-      </c>
-      <c r="D104" t="s">
-        <v>138</v>
-      </c>
-      <c r="E104" t="s">
-        <v>9</v>
-      </c>
-      <c r="F104" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
-      <c r="A105">
-        <v>19330051920214</v>
-      </c>
-      <c r="B105" t="s">
-        <v>83</v>
-      </c>
-      <c r="C105" t="s">
-        <v>108</v>
-      </c>
-      <c r="D105" t="s">
-        <v>138</v>
-      </c>
-      <c r="E105" t="s">
-        <v>8</v>
-      </c>
-      <c r="F105" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
-      <c r="A106">
-        <v>19330051920216</v>
-      </c>
-      <c r="B106" t="s">
-        <v>85</v>
-      </c>
-      <c r="C106" t="s">
-        <v>109</v>
-      </c>
-      <c r="D106" t="s">
-        <v>139</v>
-      </c>
-      <c r="E106" t="s">
-        <v>10</v>
-      </c>
-      <c r="F106" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
-      <c r="A107">
-        <v>19330051920216</v>
-      </c>
-      <c r="B107" t="s">
-        <v>85</v>
-      </c>
-      <c r="C107" t="s">
-        <v>109</v>
-      </c>
-      <c r="D107" t="s">
-        <v>139</v>
-      </c>
-      <c r="E107" t="s">
-        <v>7</v>
-      </c>
-      <c r="F107" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
-      <c r="A108">
-        <v>19330051920216</v>
-      </c>
-      <c r="B108" t="s">
-        <v>85</v>
-      </c>
-      <c r="C108" t="s">
-        <v>109</v>
-      </c>
-      <c r="D108" t="s">
-        <v>139</v>
-      </c>
-      <c r="E108" t="s">
-        <v>9</v>
-      </c>
-      <c r="F108" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="A109">
-        <v>19330051920216</v>
-      </c>
-      <c r="B109" t="s">
-        <v>85</v>
-      </c>
-      <c r="C109" t="s">
-        <v>109</v>
-      </c>
-      <c r="D109" t="s">
-        <v>139</v>
-      </c>
-      <c r="E109" t="s">
-        <v>8</v>
-      </c>
-      <c r="F109" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
-      <c r="A110">
-        <v>19330051920218</v>
-      </c>
-      <c r="B110" t="s">
-        <v>86</v>
-      </c>
-      <c r="C110" t="s">
-        <v>110</v>
-      </c>
-      <c r="D110" t="s">
-        <v>140</v>
-      </c>
-      <c r="E110" t="s">
-        <v>10</v>
-      </c>
-      <c r="F110" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
-      <c r="A111">
-        <v>19330051920218</v>
-      </c>
-      <c r="B111" t="s">
-        <v>86</v>
-      </c>
-      <c r="C111" t="s">
-        <v>110</v>
-      </c>
-      <c r="D111" t="s">
-        <v>140</v>
-      </c>
-      <c r="E111" t="s">
-        <v>7</v>
-      </c>
-      <c r="F111" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="A112">
-        <v>19330051920218</v>
-      </c>
-      <c r="B112" t="s">
-        <v>86</v>
-      </c>
-      <c r="C112" t="s">
-        <v>110</v>
-      </c>
-      <c r="D112" t="s">
-        <v>140</v>
-      </c>
-      <c r="E112" t="s">
-        <v>9</v>
-      </c>
-      <c r="F112" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="A113">
-        <v>19330051920218</v>
-      </c>
-      <c r="B113" t="s">
-        <v>86</v>
-      </c>
-      <c r="C113" t="s">
-        <v>110</v>
-      </c>
-      <c r="D113" t="s">
-        <v>140</v>
-      </c>
-      <c r="E113" t="s">
-        <v>8</v>
-      </c>
-      <c r="F113" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="A114">
-        <v>19330051920220</v>
-      </c>
-      <c r="B114" t="s">
-        <v>87</v>
-      </c>
-      <c r="C114" t="s">
-        <v>101</v>
-      </c>
-      <c r="D114" t="s">
-        <v>141</v>
-      </c>
-      <c r="E114" t="s">
-        <v>10</v>
-      </c>
-      <c r="F114" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
-      <c r="A115">
-        <v>19330051920220</v>
-      </c>
-      <c r="B115" t="s">
-        <v>87</v>
-      </c>
-      <c r="C115" t="s">
-        <v>101</v>
-      </c>
-      <c r="D115" t="s">
-        <v>141</v>
-      </c>
-      <c r="E115" t="s">
-        <v>7</v>
-      </c>
-      <c r="F115" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="A116">
-        <v>19330051920220</v>
-      </c>
-      <c r="B116" t="s">
-        <v>87</v>
-      </c>
-      <c r="C116" t="s">
-        <v>101</v>
-      </c>
-      <c r="D116" t="s">
-        <v>141</v>
-      </c>
-      <c r="E116" t="s">
-        <v>9</v>
-      </c>
-      <c r="F116" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
-      <c r="A117">
-        <v>19330051920220</v>
-      </c>
-      <c r="B117" t="s">
-        <v>87</v>
-      </c>
-      <c r="C117" t="s">
-        <v>101</v>
-      </c>
-      <c r="D117" t="s">
-        <v>141</v>
-      </c>
-      <c r="E117" t="s">
-        <v>8</v>
-      </c>
-      <c r="F117" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="A118">
-        <v>19330051920439</v>
-      </c>
-      <c r="B118" t="s">
-        <v>88</v>
-      </c>
-      <c r="C118" t="s">
-        <v>111</v>
-      </c>
-      <c r="D118" t="s">
-        <v>142</v>
-      </c>
-      <c r="E118" t="s">
-        <v>10</v>
-      </c>
-      <c r="F118" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="A119">
-        <v>19330051920439</v>
-      </c>
-      <c r="B119" t="s">
-        <v>88</v>
-      </c>
-      <c r="C119" t="s">
-        <v>111</v>
-      </c>
-      <c r="D119" t="s">
-        <v>142</v>
-      </c>
-      <c r="E119" t="s">
-        <v>7</v>
-      </c>
-      <c r="F119" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
-      <c r="A120">
-        <v>19330051920439</v>
-      </c>
-      <c r="B120" t="s">
-        <v>88</v>
-      </c>
-      <c r="C120" t="s">
-        <v>111</v>
-      </c>
-      <c r="D120" t="s">
-        <v>142</v>
-      </c>
-      <c r="E120" t="s">
-        <v>9</v>
-      </c>
-      <c r="F120" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
-      <c r="A121">
-        <v>19330051920439</v>
-      </c>
-      <c r="B121" t="s">
-        <v>88</v>
-      </c>
-      <c r="C121" t="s">
-        <v>111</v>
-      </c>
-      <c r="D121" t="s">
-        <v>142</v>
-      </c>
-      <c r="E121" t="s">
-        <v>8</v>
-      </c>
-      <c r="F121" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
-      <c r="A122">
-        <v>19330051920219</v>
-      </c>
-      <c r="B122" t="s">
-        <v>89</v>
-      </c>
-      <c r="C122" t="s">
-        <v>99</v>
-      </c>
-      <c r="D122" t="s">
-        <v>143</v>
-      </c>
-      <c r="E122" t="s">
-        <v>10</v>
-      </c>
-      <c r="F122" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="A123">
-        <v>19330051920219</v>
-      </c>
-      <c r="B123" t="s">
-        <v>89</v>
-      </c>
-      <c r="C123" t="s">
-        <v>99</v>
-      </c>
-      <c r="D123" t="s">
-        <v>143</v>
-      </c>
-      <c r="E123" t="s">
-        <v>7</v>
-      </c>
-      <c r="F123" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
-      <c r="A124">
-        <v>19330051920219</v>
-      </c>
-      <c r="B124" t="s">
-        <v>89</v>
-      </c>
-      <c r="C124" t="s">
-        <v>99</v>
-      </c>
-      <c r="D124" t="s">
-        <v>143</v>
-      </c>
-      <c r="E124" t="s">
-        <v>9</v>
-      </c>
-      <c r="F124" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="A125">
-        <v>19330051920219</v>
-      </c>
-      <c r="B125" t="s">
-        <v>89</v>
-      </c>
-      <c r="C125" t="s">
-        <v>99</v>
-      </c>
-      <c r="D125" t="s">
-        <v>143</v>
-      </c>
-      <c r="E125" t="s">
-        <v>8</v>
-      </c>
-      <c r="F125" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
-      <c r="A126">
-        <v>19330051920221</v>
-      </c>
-      <c r="B126" t="s">
-        <v>90</v>
-      </c>
-      <c r="C126" t="s">
-        <v>112</v>
-      </c>
-      <c r="D126" t="s">
-        <v>144</v>
-      </c>
-      <c r="E126" t="s">
-        <v>10</v>
-      </c>
-      <c r="F126" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="A127">
-        <v>19330051920221</v>
-      </c>
-      <c r="B127" t="s">
-        <v>90</v>
-      </c>
-      <c r="C127" t="s">
-        <v>112</v>
-      </c>
-      <c r="D127" t="s">
-        <v>144</v>
-      </c>
-      <c r="E127" t="s">
-        <v>7</v>
-      </c>
-      <c r="F127" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="A128">
-        <v>19330051920221</v>
-      </c>
-      <c r="B128" t="s">
-        <v>90</v>
-      </c>
-      <c r="C128" t="s">
-        <v>112</v>
-      </c>
-      <c r="D128" t="s">
-        <v>144</v>
-      </c>
-      <c r="E128" t="s">
-        <v>9</v>
-      </c>
-      <c r="F128" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6">
-      <c r="A129">
-        <v>19330051920221</v>
-      </c>
-      <c r="B129" t="s">
-        <v>90</v>
-      </c>
-      <c r="C129" t="s">
-        <v>112</v>
-      </c>
-      <c r="D129" t="s">
-        <v>144</v>
-      </c>
-      <c r="E129" t="s">
-        <v>8</v>
-      </c>
-      <c r="F129" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6">
-      <c r="A130">
-        <v>18330051920351</v>
-      </c>
-      <c r="B130" t="s">
-        <v>91</v>
-      </c>
-      <c r="C130" t="s">
-        <v>70</v>
-      </c>
-      <c r="D130" t="s">
-        <v>145</v>
-      </c>
-      <c r="E130" t="s">
-        <v>10</v>
-      </c>
-      <c r="F130" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
-      <c r="A131">
-        <v>18330051920351</v>
-      </c>
-      <c r="B131" t="s">
-        <v>91</v>
-      </c>
-      <c r="C131" t="s">
-        <v>70</v>
-      </c>
-      <c r="D131" t="s">
-        <v>145</v>
-      </c>
-      <c r="E131" t="s">
-        <v>7</v>
-      </c>
-      <c r="F131" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6">
-      <c r="A132">
-        <v>18330051920351</v>
-      </c>
-      <c r="B132" t="s">
-        <v>91</v>
-      </c>
-      <c r="C132" t="s">
-        <v>70</v>
-      </c>
-      <c r="D132" t="s">
-        <v>145</v>
-      </c>
-      <c r="E132" t="s">
-        <v>9</v>
-      </c>
-      <c r="F132" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
-      <c r="A133">
-        <v>18330051920351</v>
-      </c>
-      <c r="B133" t="s">
-        <v>91</v>
-      </c>
-      <c r="C133" t="s">
-        <v>70</v>
-      </c>
-      <c r="D133" t="s">
-        <v>145</v>
-      </c>
-      <c r="E133" t="s">
-        <v>8</v>
-      </c>
-      <c r="F133" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -6415,563 +3947,563 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920186</v>
+        <v>19330051920202</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
         <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920185</v>
+        <v>19330051920195</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920187</v>
+        <v>19330051920200</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920189</v>
+        <v>19330051920206</v>
       </c>
       <c r="B5" t="s">
         <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920190</v>
+        <v>19330051920207</v>
       </c>
       <c r="B6" t="s">
         <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920192</v>
+        <v>19330051920214</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920194</v>
+        <v>18330051920351</v>
       </c>
       <c r="B8" t="s">
         <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920193</v>
+        <v>19330051920186</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
         <v>120</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920195</v>
+        <v>19330051920185</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
         <v>121</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920197</v>
+        <v>19330051920187</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D11" t="s">
         <v>122</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920196</v>
+        <v>19330051920189</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D12" t="s">
         <v>123</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920198</v>
+        <v>19330051920190</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D13" t="s">
         <v>124</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920199</v>
+        <v>19330051920192</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
         <v>125</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920200</v>
+        <v>19330051920194</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D15" t="s">
         <v>126</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920201</v>
+        <v>19330051920193</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D16" t="s">
         <v>127</v>
       </c>
       <c r="E16">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920202</v>
+        <v>19330051920197</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="D17" t="s">
         <v>128</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920203</v>
+        <v>19330051920196</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D18" t="s">
         <v>129</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920204</v>
+        <v>19330051920198</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D19" t="s">
         <v>130</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920206</v>
+        <v>19330051920199</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D20" t="s">
         <v>131</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920207</v>
+        <v>19330051920201</v>
       </c>
       <c r="B21" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D21" t="s">
         <v>132</v>
       </c>
       <c r="E21">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920209</v>
+        <v>19330051920203</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="C22" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="D22" t="s">
         <v>133</v>
       </c>
       <c r="E22">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920211</v>
+        <v>19330051920204</v>
       </c>
       <c r="B23" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="D23" t="s">
         <v>134</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920215</v>
+        <v>19330051920209</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D24" t="s">
         <v>135</v>
       </c>
       <c r="E24">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920212</v>
+        <v>19330051920211</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="C25" t="s">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="D25" t="s">
         <v>136</v>
       </c>
       <c r="E25">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920213</v>
+        <v>19330051920215</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D26" t="s">
         <v>137</v>
       </c>
       <c r="E26">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920214</v>
+        <v>19330051920212</v>
       </c>
       <c r="B27" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="C27" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="D27" t="s">
         <v>138</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920216</v>
+        <v>19330051920213</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="D28" t="s">
         <v>139</v>
       </c>
       <c r="E28">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920218</v>
+        <v>19330051920216</v>
       </c>
       <c r="B29" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C29" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D29" t="s">
         <v>140</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920220</v>
+        <v>19330051920218</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="C30" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="D30" t="s">
         <v>141</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920439</v>
+        <v>19330051920220</v>
       </c>
       <c r="B31" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D31" t="s">
         <v>142</v>
       </c>
       <c r="E31">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920219</v>
+        <v>19330051920439</v>
       </c>
       <c r="B32" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="C32" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="D32" t="s">
         <v>143</v>
       </c>
       <c r="E32">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>19330051920221</v>
+        <v>19330051920219</v>
       </c>
       <c r="B33" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D33" t="s">
         <v>144</v>
       </c>
       <c r="E33">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>18330051920351</v>
+        <v>19330051920221</v>
       </c>
       <c r="B34" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="C34" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="D34" t="s">
         <v>145</v>
       </c>
       <c r="E34">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6981,7 +4513,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7011,6 +4543,236 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>19330051920195</v>
+      </c>
+      <c r="B2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>19330051920195</v>
+      </c>
+      <c r="B3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>19330051920202</v>
+      </c>
+      <c r="B4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>19330051920202</v>
+      </c>
+      <c r="B5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>18330051920351</v>
+      </c>
+      <c r="B6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>18330051920351</v>
+      </c>
+      <c r="B7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>19330051920194</v>
+      </c>
+      <c r="B8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D8" t="s">
+        <v>126</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>19330051920200</v>
+      </c>
+      <c r="B9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>19330051920206</v>
+      </c>
+      <c r="B10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>19330051920214</v>
+      </c>
+      <c r="B11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/6BLCM - Estadisticos 20212.xlsx
+++ b/grupos/6BLCM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="146">
   <si>
     <t>Materia</t>
   </si>
@@ -182,15 +182,15 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
     <t>Ángel Martínez Gerson Hermenegildo</t>
   </si>
   <si>
@@ -209,253 +209,253 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>DANNA PAOLA</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>AMABLE</t>
+  </si>
+  <si>
+    <t>ALMEIDA</t>
+  </si>
+  <si>
+    <t>BALVIN</t>
+  </si>
+  <si>
+    <t>DEMUNER</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GROTH</t>
+  </si>
+  <si>
     <t>GUILLEN</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HEREDIA</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
-    <t>LEON</t>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>LIMA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
   </si>
   <si>
     <t>MERINO</t>
   </si>
   <si>
-    <t>MIXCOHUA</t>
+    <t>NARVAEZ</t>
+  </si>
+  <si>
+    <t>PAZ</t>
   </si>
   <si>
     <t>PEREZ</t>
   </si>
   <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ROA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROSSAINZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
     <t>VELEZ</t>
   </si>
   <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>GASCA</t>
+  </si>
+  <si>
+    <t>VILLANUEVA</t>
+  </si>
+  <si>
     <t>LINARES</t>
   </si>
   <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>TLEHUACTLE</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>MORO</t>
+  </si>
+  <si>
+    <t>MARINERO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
   </si>
   <si>
     <t>VALERDE</t>
   </si>
   <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>BERMUDEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>KAREN YESSENIA</t>
+  </si>
+  <si>
+    <t>CRYSTAL MICHELL</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>ABDIEL ALFREDO</t>
+  </si>
+  <si>
+    <t>JAIR</t>
+  </si>
+  <si>
+    <t>LEYNER</t>
+  </si>
+  <si>
+    <t>ARELY</t>
+  </si>
+  <si>
+    <t>GUADALUPE ABRIL</t>
+  </si>
+  <si>
     <t>EDITH</t>
   </si>
   <si>
+    <t>KEVIN JETHZAEL</t>
+  </si>
+  <si>
+    <t>TANIA ARLETH</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>JOSE GUILLERMO</t>
+  </si>
+  <si>
     <t>MARIANA</t>
   </si>
   <si>
-    <t>DANNA PAOLA</t>
+    <t>DENISSE</t>
+  </si>
+  <si>
+    <t>GUILLERMO UBALDO</t>
+  </si>
+  <si>
+    <t>DIANA</t>
   </si>
   <si>
     <t>JULIO CESAR</t>
   </si>
   <si>
-    <t>ALEXIS</t>
+    <t>ARIEL</t>
+  </si>
+  <si>
+    <t>ASAEL PAULINO</t>
+  </si>
+  <si>
+    <t>HEIDI YAMILET</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>JANETH</t>
   </si>
   <si>
     <t>JUDITH ESTEFANIA</t>
   </si>
   <si>
+    <t>MILKA</t>
+  </si>
+  <si>
+    <t>DAYRA DENISSE</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>SARAI</t>
+  </si>
+  <si>
+    <t>ATZIN ADAO</t>
+  </si>
+  <si>
+    <t>ALAN YAMIL</t>
+  </si>
+  <si>
     <t>ROSARIO DOLORES</t>
-  </si>
-  <si>
-    <t>AMABLE</t>
-  </si>
-  <si>
-    <t>ALMEIDA</t>
-  </si>
-  <si>
-    <t>BALVIN</t>
-  </si>
-  <si>
-    <t>DEMUNER</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GROTH</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HEREDIA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>LIMA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>NARVAEZ</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ROA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROSSAINZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>GASCA</t>
-  </si>
-  <si>
-    <t>VILLANUEVA</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>MORO</t>
-  </si>
-  <si>
-    <t>MARINERO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>BERMUDEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>KAREN YESSENIA</t>
-  </si>
-  <si>
-    <t>CRYSTAL MICHELL</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>ABDIEL ALFREDO</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>LEYNER</t>
-  </si>
-  <si>
-    <t>ARELY</t>
-  </si>
-  <si>
-    <t>GUADALUPE ABRIL</t>
-  </si>
-  <si>
-    <t>KEVIN JETHZAEL</t>
-  </si>
-  <si>
-    <t>TANIA ARLETH</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>JOSE GUILLERMO</t>
-  </si>
-  <si>
-    <t>DENISSE</t>
-  </si>
-  <si>
-    <t>GUILLERMO UBALDO</t>
-  </si>
-  <si>
-    <t>DIANA</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
-  </si>
-  <si>
-    <t>ASAEL PAULINO</t>
-  </si>
-  <si>
-    <t>HEIDI YAMILET</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>JANETH</t>
-  </si>
-  <si>
-    <t>MILKA</t>
-  </si>
-  <si>
-    <t>DAYRA DENISSE</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>SARAI</t>
-  </si>
-  <si>
-    <t>ATZIN ADAO</t>
-  </si>
-  <si>
-    <t>ALAN YAMIL</t>
   </si>
 </sst>
 </file>
@@ -1566,7 +1566,7 @@
         <v>8</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F12">
         <v>10</v>
@@ -1620,7 +1620,7 @@
         <v>8</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X12">
         <v>10</v>
@@ -1951,7 +1951,7 @@
         <v>10</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F17">
         <v>8</v>
@@ -2005,7 +2005,7 @@
         <v>10</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>8</v>
@@ -2105,7 +2105,7 @@
         <v>-1</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F19">
         <v>9</v>
@@ -2159,7 +2159,7 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -2336,7 +2336,7 @@
         <v>6</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F22">
         <v>8</v>
@@ -2390,7 +2390,7 @@
         <v>6</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>8</v>
@@ -2875,7 +2875,7 @@
         <v>10</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F29">
         <v>9</v>
@@ -2929,7 +2929,7 @@
         <v>10</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X29">
         <v>9</v>
@@ -3414,7 +3414,7 @@
         <v>10</v>
       </c>
       <c r="E36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F36">
         <v>10</v>
@@ -3468,7 +3468,7 @@
         <v>10</v>
       </c>
       <c r="W36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X36">
         <v>10</v>
@@ -3530,7 +3530,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
@@ -3539,30 +3539,30 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>81.81999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>12.12</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>18.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -3571,30 +3571,30 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>87.88</v>
+        <v>93.94</v>
       </c>
       <c r="G3">
-        <v>12.12</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>9.5</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -3603,25 +3603,25 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>93.94</v>
+        <v>96.97</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="H4">
-        <v>9.5</v>
+        <v>7.8</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>6.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3727,7 +3727,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3756,162 +3756,42 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920195</v>
+        <v>19330051920202</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920200</v>
+        <v>19330051920207</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>19330051920202</v>
-      </c>
-      <c r="B4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>19330051920202</v>
-      </c>
-      <c r="B5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>19330051920206</v>
-      </c>
-      <c r="B6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" t="s">
-        <v>79</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>19330051920207</v>
-      </c>
-      <c r="B7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>19330051920214</v>
-      </c>
-      <c r="B8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D8" t="s">
-        <v>81</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>18330051920351</v>
-      </c>
-      <c r="B9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D9" t="s">
-        <v>82</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -3950,30 +3830,30 @@
         <v>19330051920202</v>
       </c>
       <c r="B2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" t="s">
         <v>65</v>
       </c>
-      <c r="C2" t="s">
-        <v>72</v>
-      </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920195</v>
+        <v>19330051920207</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -3981,98 +3861,98 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920200</v>
+        <v>19330051920186</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920206</v>
+        <v>19330051920185</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920207</v>
+        <v>19330051920187</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920214</v>
+        <v>19330051920189</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>18330051920351</v>
+        <v>19330051920190</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920186</v>
+        <v>19330051920192</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
         <v>120</v>
@@ -4083,13 +3963,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920185</v>
+        <v>19330051920194</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
         <v>121</v>
@@ -4100,13 +3980,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920187</v>
+        <v>19330051920193</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
         <v>122</v>
@@ -4117,13 +3997,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920189</v>
+        <v>19330051920195</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
         <v>123</v>
@@ -4134,13 +4014,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920190</v>
+        <v>19330051920197</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
         <v>124</v>
@@ -4151,13 +4031,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920192</v>
+        <v>19330051920196</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D14" t="s">
         <v>125</v>
@@ -4168,13 +4048,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920194</v>
+        <v>19330051920198</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
         <v>126</v>
@@ -4185,13 +4065,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920193</v>
+        <v>19330051920199</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D16" t="s">
         <v>127</v>
@@ -4202,13 +4082,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920197</v>
+        <v>19330051920200</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D17" t="s">
         <v>128</v>
@@ -4219,13 +4099,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920196</v>
+        <v>19330051920201</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D18" t="s">
         <v>129</v>
@@ -4236,13 +4116,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920198</v>
+        <v>19330051920203</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D19" t="s">
         <v>130</v>
@@ -4253,13 +4133,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920199</v>
+        <v>19330051920204</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D20" t="s">
         <v>131</v>
@@ -4270,13 +4150,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920201</v>
+        <v>19330051920206</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D21" t="s">
         <v>132</v>
@@ -4287,13 +4167,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920203</v>
+        <v>19330051920209</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="D22" t="s">
         <v>133</v>
@@ -4304,13 +4184,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920204</v>
+        <v>19330051920211</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="D23" t="s">
         <v>134</v>
@@ -4321,13 +4201,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920209</v>
+        <v>19330051920215</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s">
         <v>135</v>
@@ -4338,13 +4218,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920211</v>
+        <v>19330051920212</v>
       </c>
       <c r="B25" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="D25" t="s">
         <v>136</v>
@@ -4355,13 +4235,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920215</v>
+        <v>19330051920213</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D26" t="s">
         <v>137</v>
@@ -4372,13 +4252,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920212</v>
+        <v>19330051920214</v>
       </c>
       <c r="B27" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="D27" t="s">
         <v>138</v>
@@ -4389,13 +4269,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920213</v>
+        <v>19330051920216</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="D28" t="s">
         <v>139</v>
@@ -4406,13 +4286,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920216</v>
+        <v>19330051920218</v>
       </c>
       <c r="B29" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D29" t="s">
         <v>140</v>
@@ -4423,13 +4303,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920218</v>
+        <v>19330051920220</v>
       </c>
       <c r="B30" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C30" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="D30" t="s">
         <v>141</v>
@@ -4440,13 +4320,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920220</v>
+        <v>19330051920439</v>
       </c>
       <c r="B31" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D31" t="s">
         <v>142</v>
@@ -4457,13 +4337,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920439</v>
+        <v>19330051920219</v>
       </c>
       <c r="B32" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C32" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="D32" t="s">
         <v>143</v>
@@ -4474,13 +4354,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>19330051920219</v>
+        <v>19330051920221</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D33" t="s">
         <v>144</v>
@@ -4491,13 +4371,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>19330051920221</v>
+        <v>18330051920351</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C34" t="s">
-        <v>119</v>
+        <v>65</v>
       </c>
       <c r="D34" t="s">
         <v>145</v>
@@ -4513,7 +4393,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4548,22 +4428,22 @@
         <v>19330051920195</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4571,19 +4451,19 @@
         <v>19330051920195</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4591,25 +4471,25 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920202</v>
+        <v>19330051920194</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4617,19 +4497,19 @@
         <v>19330051920202</v>
       </c>
       <c r="B5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" t="s">
         <v>65</v>
       </c>
-      <c r="C5" t="s">
-        <v>72</v>
-      </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -4640,137 +4520,22 @@
         <v>18330051920351</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>145</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
         <v>54</v>
       </c>
       <c r="G6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>18330051920351</v>
-      </c>
-      <c r="B7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>55</v>
-      </c>
-      <c r="G7">
         <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19330051920194</v>
-      </c>
-      <c r="B8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D8" t="s">
-        <v>126</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>19330051920200</v>
-      </c>
-      <c r="B9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D9" t="s">
-        <v>77</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>19330051920206</v>
-      </c>
-      <c r="B10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" t="s">
-        <v>73</v>
-      </c>
-      <c r="D10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19330051920214</v>
-      </c>
-      <c r="B11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" t="s">
-        <v>75</v>
-      </c>
-      <c r="D11" t="s">
-        <v>81</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/6BLCM - Estadisticos 20212.xlsx
+++ b/grupos/6BLCM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="146">
   <si>
     <t>Materia</t>
   </si>
@@ -188,13 +188,13 @@
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
+    <t>Flores González Ángel</t>
+  </si>
+  <si>
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
     <t>Ángel Martínez Gerson Hermenegildo</t>
-  </si>
-  <si>
-    <t>Flores González Ángel</t>
   </si>
   <si>
     <t>NC</t>
@@ -959,16 +959,16 @@
         <v>9</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
         <v>-1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
         <v>-1</v>
@@ -1004,7 +1004,7 @@
         <v>10</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X4">
         <v>10</v>
@@ -1027,7 +1027,7 @@
         <v>10</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5">
         <v>10</v>
@@ -1036,16 +1036,16 @@
         <v>10</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J5">
         <v>-1</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
         <v>-1</v>
@@ -1081,7 +1081,7 @@
         <v>10</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X5">
         <v>10</v>
@@ -1113,16 +1113,16 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>-1</v>
@@ -1158,7 +1158,7 @@
         <v>10</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -1190,16 +1190,16 @@
         <v>10</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
         <v>-1</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X7">
         <v>10</v>
@@ -1267,16 +1267,16 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>-1</v>
@@ -1312,7 +1312,7 @@
         <v>10</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -1344,16 +1344,16 @@
         <v>10</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
         <v>-1</v>
@@ -1389,7 +1389,7 @@
         <v>9</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>9</v>
@@ -1421,16 +1421,16 @@
         <v>8</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
         <v>-1</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
         <v>-1</v>
@@ -1466,7 +1466,7 @@
         <v>10</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1498,10 +1498,10 @@
         <v>5</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
         <v>-1</v>
@@ -1575,16 +1575,16 @@
         <v>5</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
         <v>-1</v>
@@ -1611,16 +1611,16 @@
         <v>-1</v>
       </c>
       <c r="T12">
+        <v>8</v>
+      </c>
+      <c r="U12">
+        <v>8</v>
+      </c>
+      <c r="V12">
+        <v>8</v>
+      </c>
+      <c r="W12">
         <v>7</v>
-      </c>
-      <c r="U12">
-        <v>6</v>
-      </c>
-      <c r="V12">
-        <v>8</v>
-      </c>
-      <c r="W12">
-        <v>5</v>
       </c>
       <c r="X12">
         <v>10</v>
@@ -1652,16 +1652,16 @@
         <v>10</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J13">
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
         <v>-1</v>
@@ -1688,16 +1688,16 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V13">
         <v>10</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X13">
         <v>10</v>
@@ -1729,16 +1729,16 @@
         <v>9</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J14">
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
         <v>-1</v>
@@ -1774,7 +1774,7 @@
         <v>9</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -1806,16 +1806,16 @@
         <v>8</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J15">
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
         <v>-1</v>
@@ -1851,7 +1851,7 @@
         <v>9</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>10</v>
@@ -1883,16 +1883,16 @@
         <v>9</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
         <v>-1</v>
@@ -1919,16 +1919,16 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V16">
         <v>7</v>
       </c>
       <c r="W16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X16">
         <v>8</v>
@@ -1960,16 +1960,16 @@
         <v>10</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J17">
         <v>-1</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
         <v>-1</v>
@@ -2005,7 +2005,7 @@
         <v>10</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>8</v>
@@ -2037,16 +2037,16 @@
         <v>7</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J18">
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
         <v>-1</v>
@@ -2082,7 +2082,7 @@
         <v>10</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>10</v>
@@ -2114,16 +2114,16 @@
         <v>10</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
         <v>-1</v>
@@ -2159,7 +2159,7 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -2191,16 +2191,16 @@
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
         <v>-1</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L20">
         <v>-1</v>
@@ -2227,10 +2227,10 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V20">
         <v>8</v>
@@ -2268,16 +2268,16 @@
         <v>7</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J21">
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
         <v>-1</v>
@@ -2304,7 +2304,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>8</v>
@@ -2313,7 +2313,7 @@
         <v>10</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>10</v>
@@ -2345,16 +2345,16 @@
         <v>8</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
         <v>-1</v>
@@ -2381,16 +2381,16 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V22">
         <v>6</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>8</v>
@@ -2422,16 +2422,16 @@
         <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
         <v>-1</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
         <v>-1</v>
@@ -2458,16 +2458,16 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U23">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V23">
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X23">
         <v>6</v>
@@ -2499,16 +2499,16 @@
         <v>10</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
         <v>-1</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
         <v>-1</v>
@@ -2544,7 +2544,7 @@
         <v>10</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>8</v>
@@ -2576,16 +2576,16 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>-1</v>
@@ -2621,7 +2621,7 @@
         <v>10</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -2653,16 +2653,16 @@
         <v>8</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J26">
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
         <v>-1</v>
@@ -2698,7 +2698,7 @@
         <v>10</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X26">
         <v>9</v>
@@ -2730,16 +2730,16 @@
         <v>9</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
         <v>-1</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
         <v>-1</v>
@@ -2775,7 +2775,7 @@
         <v>10</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X27">
         <v>10</v>
@@ -2807,16 +2807,16 @@
         <v>8</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J28">
         <v>-1</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
         <v>-1</v>
@@ -2852,7 +2852,7 @@
         <v>8</v>
       </c>
       <c r="W28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X28">
         <v>8</v>
@@ -2884,10 +2884,10 @@
         <v>7</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
         <v>-1</v>
@@ -2961,16 +2961,16 @@
         <v>10</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
         <v>-1</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
         <v>-1</v>
@@ -3006,7 +3006,7 @@
         <v>10</v>
       </c>
       <c r="W30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X30">
         <v>10</v>
@@ -3038,16 +3038,16 @@
         <v>10</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J31">
         <v>-1</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
         <v>-1</v>
@@ -3074,16 +3074,16 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V31">
         <v>10</v>
       </c>
       <c r="W31">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X31">
         <v>10</v>
@@ -3115,16 +3115,16 @@
         <v>10</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J32">
         <v>-1</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
         <v>-1</v>
@@ -3160,7 +3160,7 @@
         <v>10</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X32">
         <v>9</v>
@@ -3192,16 +3192,16 @@
         <v>10</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J33">
         <v>-1</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
         <v>-1</v>
@@ -3228,16 +3228,16 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V33">
         <v>10</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X33">
         <v>10</v>
@@ -3269,16 +3269,16 @@
         <v>10</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J34">
         <v>-1</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
         <v>-1</v>
@@ -3314,7 +3314,7 @@
         <v>10</v>
       </c>
       <c r="W34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X34">
         <v>10</v>
@@ -3346,16 +3346,16 @@
         <v>10</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J35">
         <v>-1</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
         <v>-1</v>
@@ -3391,7 +3391,7 @@
         <v>10</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>9</v>
@@ -3423,16 +3423,16 @@
         <v>5</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J36">
         <v>-1</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L36">
         <v>-1</v>
@@ -3468,7 +3468,7 @@
         <v>10</v>
       </c>
       <c r="W36">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X36">
         <v>10</v>
@@ -3594,7 +3594,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -3603,19 +3603,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>96.97</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3626,7 +3626,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -3635,19 +3635,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>96.97</v>
+        <v>100</v>
       </c>
       <c r="G5">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3658,28 +3658,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6">
         <v>33</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>96.97</v>
+        <v>100</v>
       </c>
       <c r="G6">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3690,7 +3690,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>58</v>
@@ -4393,7 +4393,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4425,39 +4425,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920195</v>
+        <v>19330051920207</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>123</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920195</v>
+        <v>19330051920207</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>123</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -4494,47 +4494,70 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920202</v>
+        <v>19330051920195</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>18330051920351</v>
+        <v>19330051920202</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
         <v>65</v>
       </c>
       <c r="D6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>18330051920351</v>
+      </c>
+      <c r="B7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" t="s">
         <v>145</v>
       </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
         <v>54</v>
       </c>
-      <c r="G6">
+      <c r="G7">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6BLCM - Estadisticos 20212.xlsx
+++ b/grupos/6BLCM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="146">
   <si>
     <t>Materia</t>
   </si>
@@ -209,205 +209,205 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>AMABLE</t>
+  </si>
+  <si>
+    <t>ALMEIDA</t>
+  </si>
+  <si>
+    <t>BALVIN</t>
+  </si>
+  <si>
+    <t>DEMUNER</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GROTH</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUILLEN</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HEREDIA</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
     <t>LEON</t>
   </si>
   <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
+    <t>LIMA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MERINO</t>
+  </si>
+  <si>
+    <t>NARVAEZ</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ROA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROSSAINZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>VELEZ</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>GASCA</t>
+  </si>
+  <si>
+    <t>VILLANUEVA</t>
+  </si>
+  <si>
+    <t>LINARES</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>TLEHUACTLE</t>
+  </si>
+  <si>
+    <t>MORO</t>
+  </si>
+  <si>
+    <t>MARINERO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>VALERDE</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>BERMUDEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>KAREN YESSENIA</t>
+  </si>
+  <si>
+    <t>CRYSTAL MICHELL</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>ABDIEL ALFREDO</t>
+  </si>
+  <si>
+    <t>JAIR</t>
+  </si>
+  <si>
+    <t>LEYNER</t>
+  </si>
+  <si>
+    <t>ARELY</t>
+  </si>
+  <si>
+    <t>GUADALUPE ABRIL</t>
+  </si>
+  <si>
+    <t>EDITH</t>
+  </si>
+  <si>
+    <t>KEVIN JETHZAEL</t>
+  </si>
+  <si>
+    <t>TANIA ARLETH</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>JOSE GUILLERMO</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>DENISSE</t>
   </si>
   <si>
     <t>DANNA PAOLA</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>AMABLE</t>
-  </si>
-  <si>
-    <t>ALMEIDA</t>
-  </si>
-  <si>
-    <t>BALVIN</t>
-  </si>
-  <si>
-    <t>DEMUNER</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GROTH</t>
-  </si>
-  <si>
-    <t>GUILLEN</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HEREDIA</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>LIMA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MERINO</t>
-  </si>
-  <si>
-    <t>NARVAEZ</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ROA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROSSAINZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>VELEZ</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>GASCA</t>
-  </si>
-  <si>
-    <t>VILLANUEVA</t>
-  </si>
-  <si>
-    <t>LINARES</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>TLEHUACTLE</t>
-  </si>
-  <si>
-    <t>MORO</t>
-  </si>
-  <si>
-    <t>MARINERO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>VALERDE</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>BERMUDEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>KAREN YESSENIA</t>
-  </si>
-  <si>
-    <t>CRYSTAL MICHELL</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>ABDIEL ALFREDO</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>LEYNER</t>
-  </si>
-  <si>
-    <t>ARELY</t>
-  </si>
-  <si>
-    <t>GUADALUPE ABRIL</t>
-  </si>
-  <si>
-    <t>EDITH</t>
-  </si>
-  <si>
-    <t>KEVIN JETHZAEL</t>
-  </si>
-  <si>
-    <t>TANIA ARLETH</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>JOSE GUILLERMO</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>DENISSE</t>
   </si>
   <si>
     <t>GUILLERMO UBALDO</t>
@@ -965,16 +965,16 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
         <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1010,7 +1010,7 @@
         <v>10</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1042,16 +1042,16 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
         <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1119,16 +1119,16 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1196,16 +1196,16 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
         <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1273,16 +1273,16 @@
         <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
         <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1315,7 +1315,7 @@
         <v>9</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y8">
         <v>10</v>
@@ -1350,16 +1350,16 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
         <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1386,13 +1386,13 @@
         <v>10</v>
       </c>
       <c r="V9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>9</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y9">
         <v>10</v>
@@ -1427,16 +1427,16 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
         <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1469,10 +1469,10 @@
         <v>10</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1504,16 +1504,16 @@
         <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1543,7 +1543,7 @@
         <v>10</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -1581,16 +1581,16 @@
         <v>9</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
         <v>9</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1626,7 +1626,7 @@
         <v>10</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1658,16 +1658,16 @@
         <v>9</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
         <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1735,16 +1735,16 @@
         <v>9</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
         <v>9</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1771,7 +1771,7 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W14">
         <v>9</v>
@@ -1812,16 +1812,16 @@
         <v>9</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K15">
         <v>8</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1857,7 +1857,7 @@
         <v>10</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1889,16 +1889,16 @@
         <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K16">
         <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1925,7 +1925,7 @@
         <v>10</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W16">
         <v>10</v>
@@ -1934,7 +1934,7 @@
         <v>8</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1966,16 +1966,16 @@
         <v>8</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K17">
         <v>10</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2008,7 +2008,7 @@
         <v>9</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y17">
         <v>10</v>
@@ -2043,16 +2043,16 @@
         <v>9</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
         <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2088,7 +2088,7 @@
         <v>10</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2102,7 +2102,7 @@
         <v>10</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E19">
         <v>6</v>
@@ -2120,16 +2120,16 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
         <v>10</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2156,7 +2156,7 @@
         <v>10</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W19">
         <v>8</v>
@@ -2197,16 +2197,16 @@
         <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
         <v>7</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2233,7 +2233,7 @@
         <v>10</v>
       </c>
       <c r="V20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>8</v>
@@ -2274,16 +2274,16 @@
         <v>8</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
         <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2319,7 +2319,7 @@
         <v>10</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2351,16 +2351,16 @@
         <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K22">
         <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2396,7 +2396,7 @@
         <v>8</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2434,10 +2434,10 @@
         <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2470,7 +2470,7 @@
         <v>9</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2511,10 +2511,10 @@
         <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2582,16 +2582,16 @@
         <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
         <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2659,16 +2659,16 @@
         <v>9</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
         <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2701,10 +2701,10 @@
         <v>9</v>
       </c>
       <c r="X26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2736,16 +2736,16 @@
         <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
         <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2781,7 +2781,7 @@
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2813,16 +2813,16 @@
         <v>8</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K28">
         <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2849,13 +2849,13 @@
         <v>8</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>10</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>8</v>
@@ -2893,13 +2893,13 @@
         <v>-1</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2935,7 +2935,7 @@
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2967,16 +2967,16 @@
         <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
         <v>10</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3044,16 +3044,16 @@
         <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
         <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3089,7 +3089,7 @@
         <v>10</v>
       </c>
       <c r="Y31">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3121,16 +3121,16 @@
         <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K32">
         <v>10</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3163,7 +3163,7 @@
         <v>10</v>
       </c>
       <c r="X32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y32">
         <v>10</v>
@@ -3198,16 +3198,16 @@
         <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K33">
         <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3275,16 +3275,16 @@
         <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K34">
         <v>10</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3352,16 +3352,16 @@
         <v>9</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K35">
         <v>10</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3388,13 +3388,13 @@
         <v>10</v>
       </c>
       <c r="V35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W35">
         <v>9</v>
       </c>
       <c r="X35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y35">
         <v>10</v>
@@ -3429,16 +3429,16 @@
         <v>9</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K36">
         <v>9</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3474,7 +3474,7 @@
         <v>10</v>
       </c>
       <c r="Y36">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3539,19 +3539,19 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>87.88</v>
+        <v>93.94</v>
       </c>
       <c r="G2">
-        <v>12.12</v>
+        <v>6.06</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3571,25 +3571,25 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>93.94</v>
+        <v>96.97</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>6.06</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3615,7 +3615,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3647,7 +3647,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3727,7 +3727,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3756,41 +3756,21 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920202</v>
+        <v>19330051920207</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" t="s">
         <v>65</v>
-      </c>
-      <c r="D2" t="s">
-        <v>67</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>19330051920207</v>
-      </c>
-      <c r="B3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
         <v>55</v>
       </c>
     </row>
@@ -3827,16 +3807,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920202</v>
+        <v>19330051920207</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" t="s">
         <v>65</v>
-      </c>
-      <c r="D2" t="s">
-        <v>67</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -3844,30 +3824,30 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920207</v>
+        <v>19330051920186</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>114</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920186</v>
+        <v>19330051920185</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
         <v>115</v>
@@ -3878,10 +3858,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920185</v>
+        <v>19330051920187</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
         <v>95</v>
@@ -3895,10 +3875,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920187</v>
+        <v>19330051920189</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
         <v>96</v>
@@ -3912,13 +3892,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920189</v>
+        <v>19330051920190</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
         <v>118</v>
@@ -3929,13 +3909,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920190</v>
+        <v>19330051920192</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
         <v>119</v>
@@ -3946,13 +3926,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920192</v>
+        <v>19330051920194</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
         <v>120</v>
@@ -3963,10 +3943,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920194</v>
+        <v>19330051920193</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
         <v>98</v>
@@ -3980,10 +3960,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920193</v>
+        <v>19330051920195</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
         <v>99</v>
@@ -3997,10 +3977,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920195</v>
+        <v>19330051920197</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
         <v>100</v>
@@ -4014,10 +3994,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920197</v>
+        <v>19330051920196</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
         <v>101</v>
@@ -4031,10 +4011,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920196</v>
+        <v>19330051920198</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
         <v>102</v>
@@ -4048,7 +4028,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920198</v>
+        <v>19330051920199</v>
       </c>
       <c r="B15" t="s">
         <v>77</v>
@@ -4065,10 +4045,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920199</v>
+        <v>19330051920200</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
         <v>104</v>
@@ -4082,10 +4062,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920200</v>
+        <v>19330051920201</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
         <v>105</v>
@@ -4099,13 +4079,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920201</v>
+        <v>19330051920202</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="D18" t="s">
         <v>129</v>
@@ -4119,10 +4099,10 @@
         <v>19330051920203</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D19" t="s">
         <v>130</v>
@@ -4136,10 +4116,10 @@
         <v>19330051920204</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D20" t="s">
         <v>131</v>
@@ -4153,10 +4133,10 @@
         <v>19330051920206</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" t="s">
         <v>132</v>
@@ -4170,10 +4150,10 @@
         <v>19330051920209</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D22" t="s">
         <v>133</v>
@@ -4187,10 +4167,10 @@
         <v>19330051920211</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D23" t="s">
         <v>134</v>
@@ -4204,10 +4184,10 @@
         <v>19330051920215</v>
       </c>
       <c r="B24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s">
         <v>135</v>
@@ -4221,10 +4201,10 @@
         <v>19330051920212</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s">
         <v>136</v>
@@ -4238,10 +4218,10 @@
         <v>19330051920213</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D26" t="s">
         <v>137</v>
@@ -4255,10 +4235,10 @@
         <v>19330051920214</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D27" t="s">
         <v>138</v>
@@ -4272,10 +4252,10 @@
         <v>19330051920216</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D28" t="s">
         <v>139</v>
@@ -4289,10 +4269,10 @@
         <v>19330051920218</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D29" t="s">
         <v>140</v>
@@ -4306,10 +4286,10 @@
         <v>19330051920220</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D30" t="s">
         <v>141</v>
@@ -4323,10 +4303,10 @@
         <v>19330051920439</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C31" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D31" t="s">
         <v>142</v>
@@ -4340,10 +4320,10 @@
         <v>19330051920219</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C32" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D32" t="s">
         <v>143</v>
@@ -4357,10 +4337,10 @@
         <v>19330051920221</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C33" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D33" t="s">
         <v>144</v>
@@ -4374,10 +4354,10 @@
         <v>18330051920351</v>
       </c>
       <c r="B34" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C34" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="D34" t="s">
         <v>145</v>
@@ -4393,7 +4373,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4428,13 +4408,13 @@
         <v>19330051920207</v>
       </c>
       <c r="B2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" t="s">
         <v>64</v>
       </c>
-      <c r="C2" t="s">
-        <v>66</v>
-      </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -4451,13 +4431,13 @@
         <v>19330051920207</v>
       </c>
       <c r="B3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" t="s">
         <v>64</v>
       </c>
-      <c r="C3" t="s">
-        <v>66</v>
-      </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -4474,13 +4454,13 @@
         <v>19330051920194</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -4489,75 +4469,6 @@
         <v>54</v>
       </c>
       <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>19330051920195</v>
-      </c>
-      <c r="B5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D5" t="s">
-        <v>123</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>19330051920202</v>
-      </c>
-      <c r="B6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>55</v>
-      </c>
-      <c r="G6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>18330051920351</v>
-      </c>
-      <c r="B7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" t="s">
-        <v>145</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6BLCM - Estadisticos 20212.xlsx
+++ b/grupos/6BLCM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="146">
   <si>
     <t>Materia</t>
   </si>
@@ -209,214 +209,214 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>AMABLE</t>
+  </si>
+  <si>
+    <t>ALMEIDA</t>
+  </si>
+  <si>
+    <t>BALVIN</t>
+  </si>
+  <si>
+    <t>DEMUNER</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GROTH</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUILLEN</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HEREDIA</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>LIMA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MERINO</t>
+  </si>
+  <si>
     <t>MIXCOHUA</t>
   </si>
   <si>
+    <t>NARVAEZ</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ROA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROSSAINZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>VELEZ</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>GASCA</t>
+  </si>
+  <si>
+    <t>VILLANUEVA</t>
+  </si>
+  <si>
+    <t>LINARES</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>TLEHUACTLE</t>
+  </si>
+  <si>
+    <t>MORO</t>
+  </si>
+  <si>
+    <t>MARINERO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>VALERDE</t>
+  </si>
+  <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>BERMUDEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>KAREN YESSENIA</t>
+  </si>
+  <si>
+    <t>CRYSTAL MICHELL</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>ABDIEL ALFREDO</t>
+  </si>
+  <si>
+    <t>JAIR</t>
+  </si>
+  <si>
+    <t>LEYNER</t>
+  </si>
+  <si>
+    <t>ARELY</t>
+  </si>
+  <si>
+    <t>GUADALUPE ABRIL</t>
+  </si>
+  <si>
+    <t>EDITH</t>
+  </si>
+  <si>
+    <t>KEVIN JETHZAEL</t>
+  </si>
+  <si>
+    <t>TANIA ARLETH</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>JOSE GUILLERMO</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>DENISSE</t>
+  </si>
+  <si>
+    <t>DANNA PAOLA</t>
+  </si>
+  <si>
+    <t>GUILLERMO UBALDO</t>
+  </si>
+  <si>
+    <t>DIANA</t>
+  </si>
+  <si>
+    <t>JULIO CESAR</t>
+  </si>
+  <si>
     <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>AMABLE</t>
-  </si>
-  <si>
-    <t>ALMEIDA</t>
-  </si>
-  <si>
-    <t>BALVIN</t>
-  </si>
-  <si>
-    <t>DEMUNER</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GROTH</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUILLEN</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HEREDIA</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>LIMA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MERINO</t>
-  </si>
-  <si>
-    <t>NARVAEZ</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ROA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROSSAINZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>VELEZ</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>GASCA</t>
-  </si>
-  <si>
-    <t>VILLANUEVA</t>
-  </si>
-  <si>
-    <t>LINARES</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>TLEHUACTLE</t>
-  </si>
-  <si>
-    <t>MORO</t>
-  </si>
-  <si>
-    <t>MARINERO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>VALERDE</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>BERMUDEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>KAREN YESSENIA</t>
-  </si>
-  <si>
-    <t>CRYSTAL MICHELL</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>ABDIEL ALFREDO</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>LEYNER</t>
-  </si>
-  <si>
-    <t>ARELY</t>
-  </si>
-  <si>
-    <t>GUADALUPE ABRIL</t>
-  </si>
-  <si>
-    <t>EDITH</t>
-  </si>
-  <si>
-    <t>KEVIN JETHZAEL</t>
-  </si>
-  <si>
-    <t>TANIA ARLETH</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>JOSE GUILLERMO</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>DENISSE</t>
-  </si>
-  <si>
-    <t>DANNA PAOLA</t>
-  </si>
-  <si>
-    <t>GUILLERMO UBALDO</t>
-  </si>
-  <si>
-    <t>DIANA</t>
-  </si>
-  <si>
-    <t>JULIO CESAR</t>
   </si>
   <si>
     <t>ARIEL</t>
@@ -977,22 +977,22 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -1054,22 +1054,22 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -1131,22 +1131,22 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -1208,22 +1208,22 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -1285,25 +1285,25 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U8">
         <v>9</v>
@@ -1362,22 +1362,22 @@
         <v>10</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -1439,28 +1439,28 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V10">
         <v>10</v>
@@ -1516,28 +1516,28 @@
         <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V11">
         <v>10</v>
@@ -1549,7 +1549,7 @@
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1593,22 +1593,22 @@
         <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>8</v>
@@ -1620,13 +1620,13 @@
         <v>8</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>10</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1670,28 +1670,28 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>9</v>
       </c>
       <c r="U13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>10</v>
@@ -1747,28 +1747,28 @@
         <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V14">
         <v>10</v>
@@ -1824,22 +1824,22 @@
         <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>9</v>
@@ -1851,7 +1851,7 @@
         <v>9</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>10</v>
@@ -1901,22 +1901,22 @@
         <v>7</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
         <v>10</v>
@@ -1928,10 +1928,10 @@
         <v>8</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>8</v>
@@ -1978,22 +1978,22 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P17">
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>9</v>
@@ -2055,22 +2055,22 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>9</v>
@@ -2132,34 +2132,34 @@
         <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -2209,22 +2209,22 @@
         <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>10</v>
@@ -2242,7 +2242,7 @@
         <v>9</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2286,34 +2286,34 @@
         <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
         <v>8</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V21">
         <v>10</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X21">
         <v>10</v>
@@ -2363,28 +2363,28 @@
         <v>5</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>6</v>
@@ -2396,7 +2396,7 @@
         <v>8</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2410,7 +2410,7 @@
         <v>5</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E23">
         <v>8</v>
@@ -2428,7 +2428,7 @@
         <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
         <v>9</v>
@@ -2440,40 +2440,40 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
+        <v>8</v>
+      </c>
+      <c r="U23">
+        <v>8</v>
+      </c>
+      <c r="V23">
+        <v>8</v>
+      </c>
+      <c r="W23">
+        <v>9</v>
+      </c>
+      <c r="X23">
+        <v>8</v>
+      </c>
+      <c r="Y23">
         <v>7</v>
-      </c>
-      <c r="U23">
-        <v>8</v>
-      </c>
-      <c r="V23">
-        <v>-1</v>
-      </c>
-      <c r="W23">
-        <v>9</v>
-      </c>
-      <c r="X23">
-        <v>7</v>
-      </c>
-      <c r="Y23">
-        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2505,7 +2505,7 @@
         <v>7</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
         <v>10</v>
@@ -2517,22 +2517,22 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P24">
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>8</v>
@@ -2594,22 +2594,22 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2671,28 +2671,28 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P26">
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V26">
         <v>10</v>
@@ -2748,22 +2748,22 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
         <v>10</v>
@@ -2781,7 +2781,7 @@
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2825,22 +2825,22 @@
         <v>8</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P28">
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T28">
         <v>8</v>
@@ -2890,7 +2890,7 @@
         <v>6</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
         <v>6</v>
@@ -2902,40 +2902,40 @@
         <v>5</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X29">
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2979,22 +2979,22 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>10</v>
@@ -3056,28 +3056,28 @@
         <v>8</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P31">
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V31">
         <v>10</v>
@@ -3133,22 +3133,22 @@
         <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>10</v>
@@ -3210,22 +3210,22 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -3287,22 +3287,22 @@
         <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>10</v>
@@ -3364,28 +3364,28 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P35">
         <v>-1</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V35">
         <v>9</v>
@@ -3441,22 +3441,22 @@
         <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P36">
         <v>-1</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
         <v>10</v>
@@ -3539,19 +3539,19 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>93.94</v>
+        <v>100</v>
       </c>
       <c r="G2">
-        <v>6.06</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3571,25 +3571,25 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>96.97</v>
+        <v>100</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>3.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3647,7 +3647,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3679,7 +3679,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3711,7 +3711,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3727,7 +3727,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3752,26 +3752,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>19330051920207</v>
-      </c>
-      <c r="B2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -3807,30 +3787,30 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920207</v>
+        <v>19330051920186</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920186</v>
+        <v>19330051920185</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
         <v>114</v>
@@ -3841,13 +3821,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920185</v>
+        <v>19330051920187</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
         <v>115</v>
@@ -3858,13 +3838,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920187</v>
+        <v>19330051920189</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
         <v>116</v>
@@ -3875,13 +3855,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920189</v>
+        <v>19330051920190</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
         <v>117</v>
@@ -3892,13 +3872,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920190</v>
+        <v>19330051920192</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
         <v>118</v>
@@ -3909,13 +3889,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920192</v>
+        <v>19330051920194</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
         <v>119</v>
@@ -3926,13 +3906,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920194</v>
+        <v>19330051920193</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
         <v>120</v>
@@ -3943,13 +3923,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920193</v>
+        <v>19330051920195</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
         <v>121</v>
@@ -3960,13 +3940,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920195</v>
+        <v>19330051920197</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
         <v>122</v>
@@ -3977,13 +3957,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920197</v>
+        <v>19330051920196</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
         <v>123</v>
@@ -3994,13 +3974,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920196</v>
+        <v>19330051920198</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
         <v>124</v>
@@ -4011,13 +3991,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920198</v>
+        <v>19330051920199</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
         <v>125</v>
@@ -4028,13 +4008,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920199</v>
+        <v>19330051920200</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
         <v>126</v>
@@ -4045,13 +4025,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920200</v>
+        <v>19330051920201</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
         <v>127</v>
@@ -4062,13 +4042,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920201</v>
+        <v>19330051920202</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="D17" t="s">
         <v>128</v>
@@ -4079,13 +4059,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920202</v>
+        <v>19330051920203</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
         <v>129</v>
@@ -4096,13 +4076,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920203</v>
+        <v>19330051920204</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
         <v>130</v>
@@ -4113,13 +4093,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920204</v>
+        <v>19330051920206</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D20" t="s">
         <v>131</v>
@@ -4130,13 +4110,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920206</v>
+        <v>19330051920207</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
         <v>132</v>
@@ -4150,10 +4130,10 @@
         <v>19330051920209</v>
       </c>
       <c r="B22" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" t="s">
         <v>83</v>
-      </c>
-      <c r="C22" t="s">
-        <v>85</v>
       </c>
       <c r="D22" t="s">
         <v>133</v>
@@ -4167,10 +4147,10 @@
         <v>19330051920211</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D23" t="s">
         <v>134</v>
@@ -4184,10 +4164,10 @@
         <v>19330051920215</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D24" t="s">
         <v>135</v>
@@ -4201,10 +4181,10 @@
         <v>19330051920212</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D25" t="s">
         <v>136</v>
@@ -4218,10 +4198,10 @@
         <v>19330051920213</v>
       </c>
       <c r="B26" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" t="s">
         <v>85</v>
-      </c>
-      <c r="C26" t="s">
-        <v>87</v>
       </c>
       <c r="D26" t="s">
         <v>137</v>
@@ -4235,10 +4215,10 @@
         <v>19330051920214</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D27" t="s">
         <v>138</v>
@@ -4252,10 +4232,10 @@
         <v>19330051920216</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D28" t="s">
         <v>139</v>
@@ -4269,10 +4249,10 @@
         <v>19330051920218</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C29" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D29" t="s">
         <v>140</v>
@@ -4286,10 +4266,10 @@
         <v>19330051920220</v>
       </c>
       <c r="B30" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C30" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D30" t="s">
         <v>141</v>
@@ -4303,10 +4283,10 @@
         <v>19330051920439</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D31" t="s">
         <v>142</v>
@@ -4320,10 +4300,10 @@
         <v>19330051920219</v>
       </c>
       <c r="B32" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C32" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D32" t="s">
         <v>143</v>
@@ -4337,10 +4317,10 @@
         <v>19330051920221</v>
       </c>
       <c r="B33" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C33" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D33" t="s">
         <v>144</v>
@@ -4354,10 +4334,10 @@
         <v>18330051920351</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C34" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D34" t="s">
         <v>145</v>
@@ -4373,7 +4353,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4403,75 +4383,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>19330051920207</v>
-      </c>
-      <c r="B2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>19330051920207</v>
-      </c>
-      <c r="B3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>19330051920194</v>
-      </c>
-      <c r="B4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D4" t="s">
-        <v>120</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/6BLCM - Estadisticos 20212.xlsx
+++ b/grupos/6BLCM - Estadisticos 20212.xlsx
@@ -983,7 +983,7 @@
         <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
         <v>10</v>
@@ -1060,7 +1060,7 @@
         <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
         <v>10</v>
@@ -1137,7 +1137,7 @@
         <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
         <v>10</v>
@@ -1214,7 +1214,7 @@
         <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
         <v>10</v>
@@ -1291,7 +1291,7 @@
         <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
         <v>10</v>
@@ -1368,7 +1368,7 @@
         <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
         <v>9</v>
@@ -1445,7 +1445,7 @@
         <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
         <v>10</v>
@@ -1522,7 +1522,7 @@
         <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
         <v>10</v>
@@ -1599,7 +1599,7 @@
         <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
         <v>10</v>
@@ -1617,7 +1617,7 @@
         <v>8</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>8</v>
@@ -1676,7 +1676,7 @@
         <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
         <v>10</v>
@@ -1753,7 +1753,7 @@
         <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
         <v>10</v>
@@ -1830,7 +1830,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
         <v>10</v>
@@ -1907,7 +1907,7 @@
         <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -1984,7 +1984,7 @@
         <v>9</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
         <v>10</v>
@@ -2061,7 +2061,7 @@
         <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
         <v>10</v>
@@ -2138,7 +2138,7 @@
         <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -2215,7 +2215,7 @@
         <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
         <v>9</v>
@@ -2292,7 +2292,7 @@
         <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
         <v>10</v>
@@ -2369,7 +2369,7 @@
         <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
         <v>10</v>
@@ -2446,7 +2446,7 @@
         <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
         <v>9</v>
@@ -2464,7 +2464,7 @@
         <v>8</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W23">
         <v>9</v>
@@ -2523,7 +2523,7 @@
         <v>9</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
         <v>10</v>
@@ -2600,7 +2600,7 @@
         <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
         <v>10</v>
@@ -2677,7 +2677,7 @@
         <v>9</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
         <v>10</v>
@@ -2754,7 +2754,7 @@
         <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
         <v>10</v>
@@ -2831,7 +2831,7 @@
         <v>8</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
         <v>10</v>
@@ -2908,7 +2908,7 @@
         <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
         <v>10</v>
@@ -2985,7 +2985,7 @@
         <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
         <v>10</v>
@@ -3062,7 +3062,7 @@
         <v>9</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
         <v>10</v>
@@ -3139,7 +3139,7 @@
         <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
         <v>10</v>
@@ -3216,7 +3216,7 @@
         <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
         <v>10</v>
@@ -3293,7 +3293,7 @@
         <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
         <v>10</v>
@@ -3370,7 +3370,7 @@
         <v>9</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q35">
         <v>10</v>
@@ -3447,7 +3447,7 @@
         <v>10</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q36">
         <v>10</v>
@@ -3583,7 +3583,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="I3">
         <v>0</v>
